--- a/public/templates/test_input/Input_bao_cao_32.xlsx
+++ b/public/templates/test_input/Input_bao_cao_32.xlsx
@@ -759,111 +759,197 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 3</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>PX Đào lò</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn A</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>636</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L4" s="28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M4" s="28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P4" s="28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>Mất điện cục bộ 30 phút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>PX Khai thác 3</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Lê Văn C</t>
+          <t>Trần Văn B</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="28" t="n">
-        <v>873</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="I4" s="28" t="n">
+      <c r="G5" s="28" t="n">
+        <v>1124</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L5" s="28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M5" s="28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" s="28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>Không phát sinh sự cố.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>PX Đào lò</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Hoàng Văn E</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="G6" s="28" t="n">
+        <v>942</v>
+      </c>
+      <c r="H6" s="28" t="n">
         <v>15.3</v>
       </c>
-      <c r="K4" s="28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L4" s="28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M4" s="28" t="n">
+      <c r="I6" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="28" t="n">
         <v>4.3</v>
       </c>
-      <c r="N4" s="28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O4" s="28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P4" s="28" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="12" t="inlineStr">
+      <c r="M6" s="28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P6" s="28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Thiếu nhân lực ca sản xuất.</t>
+          <t>Thiết bị vận tải gặp trục trặc.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
-      <c r="K5" s="28" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" s="28" t="n"/>
-      <c r="O5" s="28" t="n"/>
-      <c r="P5" s="28" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="28" t="n"/>
-      <c r="K6" s="28" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="28" t="n"/>
-      <c r="N6" s="28" t="n"/>
-      <c r="O6" s="28" t="n"/>
-      <c r="P6" s="28" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n"/>
